--- a/NewLogic 03.05.2026/ST_UI_Track_Coder_Agent_Specification_v1.xlsx
+++ b/NewLogic 03.05.2026/ST_UI_Track_Coder_Agent_Specification_v1.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B-01 PROVENANCE" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B-02 FILE_REGISTER" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B-03 DEPENDENCY_MAP" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B-04 READ_ORDER" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B-05 HARD_RULES" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B-06 DO_NOT_MODIFY" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B-07 VALIDATION_CHECKLIST" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B-08 CONSISTENCY_AUDIT" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B-09 SEQUENCE_GATES" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B-10 ERROR_HANDLING" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="APPENDIX_A ALIAS_LOOKUP" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="APPENDIX_B SCREEN_SPEC" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="APPENDIX_C BUILD_ORDER" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SELF_CHECK" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="B-01 PROVENANCE" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="B-02 FILE_REGISTER" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="B-03 DEPENDENCY_MAP" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="B-04 READ_ORDER" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="B-05 HARD_RULES" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="B-06 DO_NOT_MODIFY" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="B-07 VALIDATION_CHECKLIST" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="B-08 CONSISTENCY_AUDIT" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="B-09 SEQUENCE_GATES" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="B-10 ERROR_HANDLING" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="APPENDIX_A ALIAS_LOOKUP" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="APPENDIX_B SCREEN_SPEC" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="APPENDIX_C BUILD_ORDER" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="SELF_CHECK" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1371,8 +1371,8 @@
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A17:D17"/>
     <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A27:D27"/>
     <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A27:D27"/>
     <mergeCell ref="A22:D22"/>
     <mergeCell ref="A20:D20"/>
     <mergeCell ref="A21:D21"/>
@@ -1733,7 +1733,7 @@
 Block 3: Compatibility 80–95 · HIGH COMPATIBILITY band (homogeneous environment). [Visual: GREEN range bar]
 Block 4: When two organisations operate inside the same interaction environment, environment-level compatibility is high by construction. The dominant resource flows, authority mechanisms, and accountability logics already align. This is the structural reason why intra-industry consolidations within the same operating archetype tend to integrate faster than cross-archetype acquisitions. What this analysis cannot tell you — and what determines whether the integration succeeds at the leadership level — is the depth of the hierarchy on each side and the type-level distribution within that hierarchy. Two {alias} organisations may share an operating logic and still produce a leadership clash if their internal type distributions differ markedly.
 Block 5 SEALED PREDICTION (timestamp UTC):
-▸ Within 30 days: 'Apparent cultural alignment masks individual-level differences. Initial integration meetings appear smooth; the surface-level recognition of shared operating logic delays the emergence of leadership conflicts that will surface at month 3.'
+▸ Within 30 days: 'Apparent cultural alignment masks role-level differences. Initial integration meetings appear smooth; the surface-level recognition of shared operating logic delays the emergence of leadership conflicts that will surface at month 3.'
 ▸ Months 2–6: 'Authority duplication crisis. Two leadership teams with the same operating logic produce competing claims to the same decision authority. The faster the cultural alignment was assumed in the first 30 days, the more brittle the response to the first authority overlap event.'
 ▸ Months 6–18: 'Hierarchy depth differential. The organisation with the deeper internal hierarchy progressively absorbs decision authority from the flatter side. If the flatter side was the buyer, the integration narrative becomes "the target is taking over from inside." This is the signature failure mode of intra-archetype mergers.'
 + verbatim Sealed Prediction caveat (see SEALED_CAVEAT row).

--- a/NewLogic 03.05.2026/ST_UI_Track_Coder_Agent_Specification_v1.xlsx
+++ b/NewLogic 03.05.2026/ST_UI_Track_Coder_Agent_Specification_v1.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="B-01 PROVENANCE" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="B-02 FILE_REGISTER" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="B-03 DEPENDENCY_MAP" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="B-04 READ_ORDER" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="B-05 HARD_RULES" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="B-06 DO_NOT_MODIFY" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="B-07 VALIDATION_CHECKLIST" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="B-08 CONSISTENCY_AUDIT" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="B-09 SEQUENCE_GATES" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="B-10 ERROR_HANDLING" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="APPENDIX_A ALIAS_LOOKUP" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="APPENDIX_B SCREEN_SPEC" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="APPENDIX_C BUILD_ORDER" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="SELF_CHECK" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B-01 PROVENANCE" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B-02 FILE_REGISTER" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B-03 DEPENDENCY_MAP" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B-04 READ_ORDER" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B-05 HARD_RULES" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B-06 DO_NOT_MODIFY" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B-07 VALIDATION_CHECKLIST" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B-08 CONSISTENCY_AUDIT" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B-09 SEQUENCE_GATES" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B-10 ERROR_HANDLING" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="APPENDIX_A ALIAS_LOOKUP" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="APPENDIX_B SCREEN_SPEC" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="APPENDIX_C BUILD_ORDER" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SELF_CHECK" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1730,7 +1730,7 @@
       <c r="E11" s="5" t="inlineStr">
         <is>
           <t>Block 2: Both organisations operate as {alias}. This pair is structurally low-friction at the environment level — the operating logic is shared. The risk shifts from cultural collision to internal hierarchy and individual differentiation.
-Block 3: Compatibility 80–95 · HIGH COMPATIBILITY band (homogeneous environment). [Visual: GREEN range bar]
+Block 3: Compatibility: {compatibilityRange} · {riskBand} band (homogeneous environment). [Visual: GREEN range bar]
 Block 4: When two organisations operate inside the same interaction environment, environment-level compatibility is high by construction. The dominant resource flows, authority mechanisms, and accountability logics already align. This is the structural reason why intra-industry consolidations within the same operating archetype tend to integrate faster than cross-archetype acquisitions. What this analysis cannot tell you — and what determines whether the integration succeeds at the leadership level — is the depth of the hierarchy on each side and the type-level distribution within that hierarchy. Two {alias} organisations may share an operating logic and still produce a leadership clash if their internal type distributions differ markedly.
 Block 5 SEALED PREDICTION (timestamp UTC):
 ▸ Within 30 days: 'Apparent cultural alignment masks role-level differences. Initial integration meetings appear smooth; the surface-level recognition of shared operating logic delays the emergence of leadership conflicts that will surface at month 3.'
